--- a/2026_09_10/User_and_POI_List.xlsx
+++ b/2026_09_10/User_and_POI_List.xlsx
@@ -1,21 +1,238 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_09_10\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA503BC-D315-4EA4-918D-4FA7F5D6A5C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
+  <si>
+    <t>RestaurantID</t>
+  </si>
+  <si>
+    <t>RestaurantName</t>
+  </si>
+  <si>
+    <t>BookingRefId</t>
+  </si>
+  <si>
+    <t>mars_userid</t>
+  </si>
+  <si>
+    <t>SubmitTime</t>
+  </si>
+  <si>
+    <t>BookingDate</t>
+  </si>
+  <si>
+    <t>BookingTime</t>
+  </si>
+  <si>
+    <t>hv_noshow</t>
+  </si>
+  <si>
+    <t>AmendedSeat</t>
+  </si>
+  <si>
+    <t>bookmenu_spending</t>
+  </si>
+  <si>
+    <t>BookingDateTime</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>UniquePOICount</t>
+  </si>
+  <si>
+    <t>Rank2</t>
+  </si>
+  <si>
+    <t>Target_Time</t>
+  </si>
+  <si>
+    <t>Nisugu</t>
+  </si>
+  <si>
+    <t>20260828923784</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>2026-08-30 12:30:00</t>
+  </si>
+  <si>
+    <t>Homeland lite</t>
+  </si>
+  <si>
+    <t>20260814611006</t>
+  </si>
+  <si>
+    <t>2026-08-14 19:30:00</t>
+  </si>
+  <si>
+    <t>Owens</t>
+  </si>
+  <si>
+    <t>20260813603319</t>
+  </si>
+  <si>
+    <t>2026-08-18 20:30:00</t>
+  </si>
+  <si>
+    <t>Coffganic</t>
+  </si>
+  <si>
+    <t>20260826876898</t>
+  </si>
+  <si>
+    <t>2026-08-28 12:45:00</t>
+  </si>
+  <si>
+    <t>Goobne Chicken</t>
+  </si>
+  <si>
+    <t>20260822805560</t>
+  </si>
+  <si>
+    <t>2026-08-22 20:00:00</t>
+  </si>
+  <si>
+    <t>佬麻雀 · 鮮湘菜</t>
+  </si>
+  <si>
+    <t>20260827911780</t>
+  </si>
+  <si>
+    <t>2026-08-28 13:00:00</t>
+  </si>
+  <si>
+    <t>20260816671636</t>
+  </si>
+  <si>
+    <t>2026-08-18 19:00:00</t>
+  </si>
+  <si>
+    <t>20260827911631-1</t>
+  </si>
+  <si>
+    <t>2026-08-28 19:00:00</t>
+  </si>
+  <si>
+    <t>GoNuts</t>
+  </si>
+  <si>
+    <t>20260825852864</t>
+  </si>
+  <si>
+    <t>2026-08-25 13:30:00</t>
+  </si>
+  <si>
+    <t>20260826888812</t>
+  </si>
+  <si>
+    <t>2026-08-31 13:00:00</t>
+  </si>
+  <si>
+    <t>20260816668201</t>
+  </si>
+  <si>
+    <t>2026-08-16 20:30:00</t>
+  </si>
+  <si>
+    <t>神燈海鮮酒家</t>
+  </si>
+  <si>
+    <t>20260828933539-1</t>
+  </si>
+  <si>
+    <t>2026-08-29 12:00:00</t>
+  </si>
+  <si>
+    <t>20260813603188-1</t>
+  </si>
+  <si>
+    <t>2026-08-13 20:00:00</t>
+  </si>
+  <si>
+    <t>自己人</t>
+  </si>
+  <si>
+    <t>20260823822383</t>
+  </si>
+  <si>
+    <t>2026-08-23 18:30:00</t>
+  </si>
+  <si>
+    <t>品越越式料理</t>
+  </si>
+  <si>
+    <t>20260827914531</t>
+  </si>
+  <si>
+    <t>2026-08-28 19:15:00</t>
+  </si>
+  <si>
+    <t>Marco's Oyster Bar &amp; Grill</t>
+  </si>
+  <si>
+    <t>20260827914423-2</t>
+  </si>
+  <si>
+    <t>2026-08-30 18:00:00</t>
+  </si>
+  <si>
+    <t>20260824848902</t>
+  </si>
+  <si>
+    <t>2026-08-26 14:00:00</t>
+  </si>
+  <si>
+    <t>20260819723100</t>
+  </si>
+  <si>
+    <t>2026-08-23 13:00:00</t>
+  </si>
+  <si>
+    <t>20260827914572</t>
+  </si>
+  <si>
+    <t>20260817674520</t>
+  </si>
+  <si>
+    <t>2026-08-17 11:00:00</t>
+  </si>
+  <si>
+    <t>Award User</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="hh:mm:ss"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd hh:mm:ss"/>
-    <numFmt numFmtId="169" formatCode="[h]:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23,18 +240,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="1">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,113 +267,388 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0"/>
-    <xf numFmtId="166" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" xfId="0" applyNumberFormat="1"/>
-    <xf xfId="0" fontId="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" builtinId="0" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>RestaurantID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>RestaurantName</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>BookingRefId</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>mars_userid</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>SubmitTime</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>BookingDate</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>BookingTime</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>hv_noshow</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>AmendedSeat</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>bookmenu_spending</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>BookingDateTime</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>UniquePOICount</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Rank2</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Target_Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>120815</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nisugu</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20260828923784</t>
-        </is>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
       </c>
       <c r="D2">
         <v>169</v>
@@ -167,20 +660,16 @@
         <v>46264</v>
       </c>
       <c r="G2" s="2">
-        <v>0.5208333333333334</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-08-30 12:30:00</t>
-        </is>
+      <c r="K2" t="s">
+        <v>18</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -192,19 +681,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>23198</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Homeland lite</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>20260814611006</t>
-        </is>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
       </c>
       <c r="D3">
         <v>178015</v>
@@ -218,18 +703,14 @@
       <c r="G3" s="2">
         <v>0.8125</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="H3" t="s">
+        <v>17</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-08-14 19:30:00</t>
-        </is>
+      <c r="K3" t="s">
+        <v>21</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -241,44 +722,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>32778</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Owens</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20260813603319</t>
-        </is>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
       </c>
       <c r="D4">
         <v>226418</v>
       </c>
       <c r="E4" s="3">
-        <v>46247.80280092593</v>
+        <v>46247.802800925929</v>
       </c>
       <c r="F4" s="1">
         <v>46252</v>
       </c>
       <c r="G4" s="2">
-        <v>0.8541666666666666</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-08-18 20:30:00</t>
-        </is>
+      <c r="K4" t="s">
+        <v>24</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -290,25 +763,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>152339</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Coffganic</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>20260826876898</t>
-        </is>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
       </c>
       <c r="D5">
         <v>546396</v>
       </c>
       <c r="E5" s="3">
-        <v>46260.48384965278</v>
+        <v>46260.483849652781</v>
       </c>
       <c r="F5" s="1">
         <v>46262</v>
@@ -316,18 +785,14 @@
       <c r="G5" s="2">
         <v>0.53125</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="H5" t="s">
+        <v>17</v>
       </c>
       <c r="I5">
         <v>3</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:45:00</t>
-        </is>
+      <c r="K5" t="s">
+        <v>27</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -339,44 +804,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6017</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Goobne Chicken</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20260822805560</t>
-        </is>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
       </c>
       <c r="D6">
         <v>561943</v>
       </c>
       <c r="E6" s="3">
-        <v>46256.80107954861</v>
+        <v>46256.801079548612</v>
       </c>
       <c r="F6" s="1">
         <v>46256</v>
       </c>
       <c r="G6" s="2">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-08-22 20:00:00</t>
-        </is>
+      <c r="K6" t="s">
+        <v>30</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -388,44 +845,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>128445</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>佬麻雀 · 鮮湘菜</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20260827911780</t>
-        </is>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
       </c>
       <c r="D7">
         <v>561943</v>
       </c>
       <c r="E7" s="3">
-        <v>46261.8943380787</v>
+        <v>46261.894338078702</v>
       </c>
       <c r="F7" s="1">
         <v>46262</v>
       </c>
       <c r="G7" s="2">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-08-28 13:00:00</t>
-        </is>
+      <c r="K7" t="s">
+        <v>33</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -436,50 +885,40 @@
       <c r="N7">
         <v>2</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-08-28 13:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="O7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>32778</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Owens</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20260816671636</t>
-        </is>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
       </c>
       <c r="D8">
         <v>632065</v>
       </c>
       <c r="E8" s="3">
-        <v>46250.9735849537</v>
+        <v>46250.973584953703</v>
       </c>
       <c r="F8" s="1">
         <v>46252</v>
       </c>
       <c r="G8" s="2">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-08-18 19:00:00</t>
-        </is>
+      <c r="K8" t="s">
+        <v>35</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -491,44 +930,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6018</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Goobne Chicken</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20260827911631-1</t>
-        </is>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
       </c>
       <c r="D9">
         <v>901198</v>
       </c>
       <c r="E9" s="3">
-        <v>46261.91156655092</v>
+        <v>46261.911566550923</v>
       </c>
       <c r="F9" s="1">
         <v>46262</v>
       </c>
       <c r="G9" s="2">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
       </c>
       <c r="I9">
         <v>3</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-08-28 19:00:00</t>
-        </is>
+      <c r="K9" t="s">
+        <v>37</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -540,19 +971,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>120833</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GoNuts</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>20260825852864</t>
-        </is>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
       </c>
       <c r="D10">
         <v>1149565</v>
@@ -566,18 +993,14 @@
       <c r="G10" s="2">
         <v>0.5625</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="H10" t="s">
+        <v>17</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:30:00</t>
-        </is>
+      <c r="K10" t="s">
+        <v>40</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -589,19 +1012,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>120815</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Nisugu</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>20260826888812</t>
-        </is>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
       </c>
       <c r="D11">
         <v>1149565</v>
@@ -613,20 +1032,16 @@
         <v>46265</v>
       </c>
       <c r="G11" s="2">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:00:00</t>
-        </is>
+      <c r="K11" t="s">
+        <v>42</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -637,50 +1052,40 @@
       <c r="N11">
         <v>2</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="O11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>32778</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Owens</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>20260816668201</t>
-        </is>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
       </c>
       <c r="D12">
         <v>1492404</v>
       </c>
       <c r="E12" s="3">
-        <v>46250.81219606481</v>
+        <v>46250.812196064813</v>
       </c>
       <c r="F12" s="1">
         <v>46250</v>
       </c>
       <c r="G12" s="2">
-        <v>0.8541666666666666</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
       </c>
       <c r="I12">
         <v>2</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-08-16 20:30:00</t>
-        </is>
+      <c r="K12" t="s">
+        <v>44</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -692,19 +1097,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>109820</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>神燈海鮮酒家</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>20260828933539-1</t>
-        </is>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
       </c>
       <c r="D13">
         <v>1511207</v>
@@ -718,18 +1119,14 @@
       <c r="G13" s="2">
         <v>0.5</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="H13" t="s">
+        <v>17</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-08-29 12:00:00</t>
-        </is>
+      <c r="K13" t="s">
+        <v>47</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -741,19 +1138,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>32778</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Owens</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>20260813603188-1</t>
-        </is>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
       </c>
       <c r="D14">
         <v>2198099</v>
@@ -765,20 +1158,16 @@
         <v>46247</v>
       </c>
       <c r="G14" s="2">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-08-13 20:00:00</t>
-        </is>
+      <c r="K14" t="s">
+        <v>49</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -790,44 +1179,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>127527</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>自己人</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>20260823822383</t>
-        </is>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
       </c>
       <c r="D15">
         <v>2662581</v>
       </c>
       <c r="E15" s="3">
-        <v>46257.74816423611</v>
+        <v>46257.748164236109</v>
       </c>
       <c r="F15" s="1">
         <v>46257</v>
       </c>
       <c r="G15" s="2">
-        <v>0.7708333333333334</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-08-23 18:30:00</t>
-        </is>
+      <c r="K15" t="s">
+        <v>52</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -839,44 +1220,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3315</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>品越越式料理</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>20260827914531</t>
-        </is>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
       </c>
       <c r="D16">
         <v>4007358</v>
       </c>
       <c r="E16" s="3">
-        <v>46261.99432896991</v>
+        <v>46261.994328969908</v>
       </c>
       <c r="F16" s="1">
         <v>46262</v>
       </c>
       <c r="G16" s="2">
-        <v>0.8020833333333334</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-08-28 19:15:00</t>
-        </is>
+      <c r="K16" t="s">
+        <v>55</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -888,19 +1261,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14857</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Marco's Oyster Bar &amp; Grill</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>20260827914423-2</t>
-        </is>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
       </c>
       <c r="D17">
         <v>4007358</v>
@@ -914,18 +1283,14 @@
       <c r="G17" s="2">
         <v>0.75</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="H17" t="s">
+        <v>17</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-08-30 18:00:00</t>
-        </is>
+      <c r="K17" t="s">
+        <v>58</v>
       </c>
       <c r="L17">
         <v>1</v>
@@ -936,50 +1301,40 @@
       <c r="N17">
         <v>2</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2026-08-30 18:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="O17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>60020</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Goobne Chicken</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>20260824848902</t>
-        </is>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
       </c>
       <c r="D18">
         <v>4055384</v>
       </c>
       <c r="E18" s="3">
-        <v>46258.96747711806</v>
+        <v>46258.967477118058</v>
       </c>
       <c r="F18" s="1">
         <v>46260</v>
       </c>
       <c r="G18" s="2">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
       </c>
       <c r="I18">
         <v>3</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-08-26 14:00:00</t>
-        </is>
+      <c r="K18" t="s">
+        <v>60</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -991,44 +1346,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6017</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Goobne Chicken</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>20260819723100</t>
-        </is>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
       </c>
       <c r="D19">
         <v>4338046</v>
       </c>
       <c r="E19" s="3">
-        <v>46253.45445648148</v>
+        <v>46253.454456481479</v>
       </c>
       <c r="F19" s="1">
         <v>46257</v>
       </c>
       <c r="G19" s="2">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-08-23 13:00:00</t>
-        </is>
+      <c r="K19" t="s">
+        <v>62</v>
       </c>
       <c r="L19">
         <v>1</v>
@@ -1040,19 +1387,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3315</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>品越越式料理</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>20260827914572</t>
-        </is>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
       </c>
       <c r="D20">
         <v>4496106</v>
@@ -1064,20 +1407,16 @@
         <v>46262</v>
       </c>
       <c r="G20" s="2">
-        <v>0.8020833333333334</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-08-28 19:15:00</t>
-        </is>
+      <c r="K20" t="s">
+        <v>55</v>
       </c>
       <c r="L20">
         <v>1</v>
@@ -1089,44 +1428,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>134580</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>自己人</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>20260817674520</t>
-        </is>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
       </c>
       <c r="D21">
         <v>6835969</v>
       </c>
       <c r="E21" s="3">
-        <v>46251.39449540509</v>
+        <v>46251.394495405089</v>
       </c>
       <c r="F21" s="1">
         <v>46251</v>
       </c>
       <c r="G21" s="2">
-        <v>0.4583333333333333</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
       </c>
       <c r="I21">
         <v>3</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:00:00</t>
-        </is>
+      <c r="K21" t="s">
+        <v>65</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -1138,6 +1469,314 @@
         <v>1</v>
       </c>
     </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>6</v>
+      </c>
+      <c r="H26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" t="s">
+        <v>11</v>
+      </c>
+      <c r="M26" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" t="s">
+        <v>13</v>
+      </c>
+      <c r="O26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>6017</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27">
+        <v>561943</v>
+      </c>
+      <c r="E27" s="3">
+        <v>46256.801079548612</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46256</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>128445</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28">
+        <v>561943</v>
+      </c>
+      <c r="E28" s="3">
+        <v>46261.894338078702</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46262</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>120833</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29">
+        <v>1149565</v>
+      </c>
+      <c r="E29" s="3">
+        <v>46259.419567164354</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46259</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>40</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>120815</v>
+      </c>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30">
+        <v>1149565</v>
+      </c>
+      <c r="E30" s="3">
+        <v>46260.833312118055</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46265</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>42</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>3315</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31">
+        <v>4007358</v>
+      </c>
+      <c r="E31" s="3">
+        <v>46261.994328969908</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46262</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>2</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>14857</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32">
+        <v>4007358</v>
+      </c>
+      <c r="E32" s="3">
+        <v>46262.837966203704</v>
+      </c>
+      <c r="F32" s="1">
+        <v>46264</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>